--- a/AAII_Financials/Quarterly/GAN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GAN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
   <si>
     <t>GAN</t>
   </si>
@@ -656,261 +656,267 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43281</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43100</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>42916</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>42735</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>42551</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>30700</v>
+      </c>
+      <c r="E8" s="3">
         <v>29800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>33800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>35100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>36900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>32100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>35000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>37500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>30400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>32300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>34400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>27100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>35200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>10300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>30000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>14000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5000</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>4800</v>
       </c>
       <c r="Z8" s="3">
         <v>4800</v>
       </c>
       <c r="AA8" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AB8" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E9" s="3">
         <v>9200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>9400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>11700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>11500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>8700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>18500</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V9" s="3">
         <v>11900</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>5</v>
       </c>
@@ -926,68 +932,71 @@
       <c r="AA9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E10" s="3">
         <v>20600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>24300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>24900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>26900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>22700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>24500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>25800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>18900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>21500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>24000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>18400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>24700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>11500</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V10" s="3">
         <v>2100</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1003,8 +1012,11 @@
       <c r="AA10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1032,62 +1044,63 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E12" s="3">
         <v>9200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>11200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>9600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>7200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>9000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>7000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>11000</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S12" s="3">
+      <c r="S12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T12" s="3">
         <v>3400</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>5</v>
       </c>
@@ -1109,8 +1122,11 @@
       <c r="AA12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1186,49 +1202,52 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>8400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-9300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>137100</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>29600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3500</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>5</v>
@@ -1236,18 +1255,18 @@
       <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
         <v>1700</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3">
         <v>300</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1263,64 +1282,67 @@
       <c r="AA14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E15" s="3">
         <v>4300</v>
-      </c>
-      <c r="E15" s="3">
-        <v>4200</v>
       </c>
       <c r="F15" s="3">
         <v>4200</v>
       </c>
       <c r="G15" s="3">
+        <v>4200</v>
+      </c>
+      <c r="H15" s="3">
         <v>6400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3300</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q15" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S15" s="3">
+      <c r="S15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T15" s="3">
         <v>4300</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U15" s="3">
-        <v>0</v>
+      <c r="U15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V15" s="3">
         <v>0</v>
@@ -1340,8 +1362,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1366,162 +1391,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>40200</v>
+      </c>
+      <c r="E17" s="3">
         <v>37000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>50700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>31800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>182400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>37300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>72700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>41600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>46800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>39400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>37100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>32100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>54600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>16600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>27400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>22200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-7200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-16900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-145500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-37700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-16400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-19400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-8300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-8200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1549,13 +1581,14 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1564,56 +1597,56 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>1200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-800</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-300</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
@@ -1626,111 +1659,117 @@
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-12700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>7500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-137900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-32000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-11800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-16300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3">
         <v>7000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3">
         <v>1300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1700</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3">
         <v>1100</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1742,200 +1781,209 @@
         <v>0</v>
       </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>400</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T22" s="3">
         <v>200</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X22" s="3">
         <v>200</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="3" t="s">
-        <v>5</v>
+      <c r="Y22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-17800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-144300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-38600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-16000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-19900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-8600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-8600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-3400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-900</v>
-      </c>
-      <c r="V24" s="3">
-        <v>-400</v>
       </c>
       <c r="W24" s="3">
         <v>-400</v>
       </c>
       <c r="X24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Y24" s="3">
         <v>-500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2011,162 +2059,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-18400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-147700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-38300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-12500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-8700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-20200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-8800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-7700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-18400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-147700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-38300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-12500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-8700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-20200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-8800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-7700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2242,8 +2299,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2319,8 +2379,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2396,8 +2459,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2473,13 +2539,16 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -2488,56 +2557,56 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-1200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>800</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>300</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
@@ -2550,85 +2619,91 @@
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-18400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-147700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-38300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-12500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-8700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-20200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-8800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2704,167 +2779,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-18400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-147700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-38300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-12500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-8700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-20200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-8800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43281</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43100</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>42916</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>42735</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>42551</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2892,8 +2976,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2921,85 +3006,89 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E41" s="3">
         <v>39200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>43400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>40800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>45900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>41800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>49100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>33600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>39500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>50300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>52100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>52200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>152700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>57500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>63800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3075,85 +3164,91 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E43" s="3">
         <v>9200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>13900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>13800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>13100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7400</v>
-      </c>
-      <c r="M43" s="3">
-        <v>12200</v>
       </c>
       <c r="N43" s="3">
         <v>12200</v>
       </c>
       <c r="O43" s="3">
+        <v>12200</v>
+      </c>
+      <c r="P43" s="3">
         <v>8100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>9200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>12700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>9100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4800</v>
-      </c>
-      <c r="Z43" s="3">
-        <v>3500</v>
       </c>
       <c r="AA43" s="3">
         <v>3500</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3190,201 +3285,210 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P44" s="3">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q44" s="3">
         <v>400</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>800</v>
       </c>
       <c r="R44" s="3">
         <v>800</v>
       </c>
       <c r="S44" s="3">
+        <v>800</v>
+      </c>
+      <c r="T44" s="3">
         <v>900</v>
       </c>
-      <c r="T44" s="3">
-        <v>0</v>
-      </c>
       <c r="U44" s="3">
+        <v>0</v>
+      </c>
+      <c r="V44" s="3">
         <v>1200</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
-      </c>
-      <c r="W44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z44" s="3">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+      <c r="X44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA44" s="3">
         <v>100</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>7400</v>
+        <v>6500</v>
       </c>
       <c r="E45" s="3">
         <v>7400</v>
       </c>
       <c r="F45" s="3">
+        <v>7400</v>
+      </c>
+      <c r="G45" s="3">
         <v>8400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>7900</v>
       </c>
       <c r="H45" s="3">
         <v>7900</v>
       </c>
       <c r="I45" s="3">
+        <v>7900</v>
+      </c>
+      <c r="J45" s="3">
         <v>7000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1100</v>
-      </c>
-      <c r="W45" s="3">
-        <v>1200</v>
       </c>
       <c r="X45" s="3">
         <v>1200</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>5</v>
+      <c r="Y45" s="3">
+        <v>1200</v>
       </c>
       <c r="Z45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>56500</v>
+      </c>
+      <c r="E46" s="3">
         <v>55800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>60900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>63100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>67600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>62900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>67400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>49200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>54400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>62500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>68800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>70600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>163500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>70200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>72800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>18000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>18800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>17000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>13800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>9200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>8100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>9600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>8700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>8500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3421,14 +3525,14 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P47" s="3">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q47" s="3">
         <v>300</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>100</v>
       </c>
       <c r="R47" s="3">
         <v>100</v>
@@ -3436,8 +3540,8 @@
       <c r="S47" s="3">
         <v>100</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>5</v>
+      <c r="T47" s="3">
+        <v>100</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>5</v>
@@ -3445,8 +3549,8 @@
       <c r="V47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X47" s="3">
         <v>0</v>
@@ -3460,162 +3564,171 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E48" s="3">
         <v>4400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2100</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H48" s="3">
         <v>2900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2400</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L48" s="3">
         <v>3300</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P48" s="3">
         <v>2100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E49" s="3">
         <v>23300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>26800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>29900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>31700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>162900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>174200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>191800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>196500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>200900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>206500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>204300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>7100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>10300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>7200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>7700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>7900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>7400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3691,8 +3804,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3768,49 +3884,52 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E52" s="3">
         <v>5200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>13000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>500</v>
-      </c>
-      <c r="P52" s="3">
-        <v>100</v>
       </c>
       <c r="Q52" s="3">
         <v>100</v>
@@ -3819,34 +3938,37 @@
         <v>100</v>
       </c>
       <c r="S52" s="3">
+        <v>100</v>
+      </c>
+      <c r="T52" s="3">
         <v>800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>200</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
-      </c>
       <c r="W52" s="3">
         <v>0</v>
       </c>
       <c r="X52" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Y52" s="3">
         <v>200</v>
       </c>
       <c r="Z52" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="AA52" s="3">
         <v>800</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3922,85 +4044,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>87500</v>
+      </c>
+      <c r="E54" s="3">
         <v>88700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>95000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>96600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>103100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>230100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>246000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>250700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>260900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>276400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>283000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>278800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>173200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>78000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>79900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>24500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>26200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>23100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>22600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>15300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>15800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>17900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>17400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>17600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4028,8 +4156,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4057,85 +4186,89 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E57" s="3">
         <v>5400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6400</v>
-      </c>
-      <c r="H57" s="3">
-        <v>6300</v>
       </c>
       <c r="I57" s="3">
         <v>6300</v>
       </c>
       <c r="J57" s="3">
+        <v>6300</v>
+      </c>
+      <c r="K57" s="3">
         <v>5800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>13400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>9100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4169,38 +4302,38 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O58" s="3">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P58" s="3">
         <v>100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>300</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>500</v>
       </c>
       <c r="R58" s="3">
         <v>500</v>
       </c>
       <c r="S58" s="3">
+        <v>500</v>
+      </c>
+      <c r="T58" s="3">
         <v>900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>300</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
-      <c r="X58" s="3" t="s">
-        <v>5</v>
+      <c r="X58" s="3">
+        <v>0</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>5</v>
@@ -4211,186 +4344,195 @@
       <c r="AA58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E59" s="3">
         <v>27000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>27500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>25400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>26100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>20300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>21200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>24200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>27800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>28700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>24600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>21200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1300</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E60" s="3">
         <v>32500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>32300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>31000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>32500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>26700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>27400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>30000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>33000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>33300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>28800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>25500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>17300</v>
-      </c>
-      <c r="P60" s="3">
-        <v>15200</v>
       </c>
       <c r="Q60" s="3">
         <v>15200</v>
       </c>
       <c r="R60" s="3">
+        <v>15200</v>
+      </c>
+      <c r="S60" s="3">
         <v>9100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>12300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>42200</v>
+      </c>
+      <c r="E61" s="3">
         <v>41100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>39800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>28500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>28200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>27900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>27700</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -4407,120 +4549,126 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="3">
         <v>400</v>
       </c>
       <c r="R61" s="3">
+        <v>400</v>
+      </c>
+      <c r="S61" s="3">
         <v>500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2500</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E62" s="3">
         <v>13100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>12600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>21600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>23200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>21900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>400</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S62" s="3">
+      <c r="S62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T62" s="3">
         <v>700</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
-      </c>
-      <c r="U62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V62" s="3">
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W62" s="3">
         <v>300</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
-      </c>
       <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3">
         <v>200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>300</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>400</v>
       </c>
       <c r="AA62" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4596,8 +4744,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4673,8 +4824,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4750,85 +4904,91 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>92100</v>
+      </c>
+      <c r="E66" s="3">
         <v>86600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>85000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>72000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>82300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>77700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>77000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>33700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>36900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>37200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>32500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>29400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>17700</v>
-      </c>
-      <c r="P66" s="3">
-        <v>15600</v>
       </c>
       <c r="Q66" s="3">
         <v>15600</v>
       </c>
       <c r="R66" s="3">
+        <v>15600</v>
+      </c>
+      <c r="S66" s="3">
         <v>9600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>11000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>12900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>10600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>6800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4856,8 +5016,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4933,8 +5094,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5010,8 +5174,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5087,8 +5254,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5164,85 +5334,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-309300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-299900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-291800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-273400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-274900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-127200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-120200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-80900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-76400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-63800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-55100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-51400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-45800</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R72" s="3">
+      <c r="R72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S72" s="3">
         <v>-21900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-23000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-16900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-25300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-14800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-14700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-13000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-10600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-8900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-6100</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5318,8 +5494,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5395,8 +5574,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5472,85 +5654,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E76" s="3">
         <v>2000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>24600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>152400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>169000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>217000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>224000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>239200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>250400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>249400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>155600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>62400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>64300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>15100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>10200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>12200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>11100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>13500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5626,167 +5814,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43281</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43100</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>42916</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>42735</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>42551</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-18400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-147700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-38300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-12500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-8700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-20200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-8800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5814,85 +6011,89 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E83" s="3">
         <v>4300</v>
-      </c>
-      <c r="E83" s="3">
-        <v>4200</v>
       </c>
       <c r="F83" s="3">
         <v>4200</v>
       </c>
       <c r="G83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="H83" s="3">
         <v>6400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3200</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3">
         <v>4700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>6200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5968,8 +6169,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6045,8 +6249,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6122,8 +6329,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6199,8 +6409,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6276,85 +6489,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-6300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
         <v>6300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>5300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-200</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
       <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6382,74 +6601,75 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1200</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-1800</v>
       </c>
       <c r="F91" s="3">
         <v>-1800</v>
       </c>
       <c r="G91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="H91" s="3">
         <v>-1100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>1400</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S91" s="3">
-        <v>-200</v>
+      <c r="S91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T91" s="3">
         <v>-200</v>
       </c>
       <c r="U91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
       <c r="Y91" s="3">
         <v>0</v>
       </c>
@@ -6457,10 +6677,13 @@
         <v>0</v>
       </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6536,8 +6759,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6613,85 +6839,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1200</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-1800</v>
       </c>
       <c r="F94" s="3">
         <v>-1800</v>
       </c>
       <c r="G94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="H94" s="3">
         <v>-1600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8500</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-4000</v>
       </c>
       <c r="K94" s="3">
         <v>-4000</v>
       </c>
       <c r="L94" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-94600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
         <v>-2900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6719,8 +6951,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6796,8 +7029,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6873,8 +7109,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6950,8 +7189,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7027,235 +7269,247 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>1300</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>27000</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>500</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>154700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-400</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
         <v>200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>5700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>5200</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>2500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>3200</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>400</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
         <v>300</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>-100</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
         <v>0</v>
       </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>300</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>15500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-10800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-100500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>142400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
         <v>3200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-4700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GAN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GAN_QTR_FIN.xlsx
@@ -656,127 +656,131 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43100</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>42916</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>42735</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>42551</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -784,142 +788,145 @@
         <v>30700</v>
       </c>
       <c r="E8" s="3">
+        <v>30700</v>
+      </c>
+      <c r="F8" s="3">
         <v>29800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>33800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>35100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>36900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>32100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>35000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>37500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>30400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>32300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>34400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>27100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>35200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>30000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>11300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>14000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5000</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>4800</v>
       </c>
       <c r="AA8" s="3">
         <v>4800</v>
       </c>
       <c r="AB8" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AC8" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E9" s="3">
         <v>9800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>10200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>9400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>11700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>11500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>18500</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V9" s="3">
+      <c r="V9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W9" s="3">
         <v>11900</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>5</v>
       </c>
@@ -935,71 +942,74 @@
       <c r="AB9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E10" s="3">
         <v>20900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>20600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>24300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>24900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>26900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>22700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>24500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>25800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>18900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>21500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>24000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>18400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>24700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>6400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>5400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>11500</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="V10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W10" s="3">
         <v>2100</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1015,8 +1025,11 @@
       <c r="AB10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1045,65 +1058,66 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E12" s="3">
         <v>8300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>9200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>11200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>9600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>7200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>9000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>7000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>11000</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T12" s="3">
+      <c r="T12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U12" s="3">
         <v>3400</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>5</v>
       </c>
@@ -1125,8 +1139,11 @@
       <c r="AB12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1205,52 +1222,55 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>900</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>8400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-9300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>137100</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>29600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3500</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>5</v>
@@ -1258,18 +1278,18 @@
       <c r="S14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="3">
         <v>1700</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W14" s="3">
         <v>300</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1285,67 +1305,70 @@
       <c r="AB14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E15" s="3">
         <v>4400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4300</v>
-      </c>
-      <c r="F15" s="3">
-        <v>4200</v>
       </c>
       <c r="G15" s="3">
         <v>4200</v>
       </c>
       <c r="H15" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I15" s="3">
         <v>6400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>6600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3300</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R15" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T15" s="3">
+      <c r="T15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U15" s="3">
         <v>4300</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V15" s="3">
-        <v>0</v>
+      <c r="V15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
@@ -1365,8 +1388,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1392,168 +1418,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>33900</v>
+      </c>
+      <c r="E17" s="3">
         <v>40200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>37000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>50700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>31800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>182400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>37300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>72700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>41600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>46800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>39400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>37100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>32100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>54600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>16600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>27400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>22200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-9500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-7200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-16900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-145500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-37700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-16400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-19400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-8300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-8200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1582,17 +1615,18 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
@@ -1600,56 +1634,56 @@
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>1200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-800</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-300</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
@@ -1662,117 +1696,123 @@
       <c r="AB20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-5200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-12700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>7500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-137900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-32000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-11800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-16300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-3900</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U21" s="3">
         <v>7000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E22" s="3">
+      <c r="D22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3">
         <v>1300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1700</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3">
         <v>1100</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1784,126 +1824,132 @@
         <v>0</v>
       </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>400</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T22" s="3">
+      <c r="T22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U22" s="3">
         <v>200</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y22" s="3">
         <v>200</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="3" t="s">
-        <v>5</v>
+      <c r="Z22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>0</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-17800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-144300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-6600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-38600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-16000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-19900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-8600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-8600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1911,79 +1957,82 @@
         <v>-200</v>
       </c>
       <c r="E24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F24" s="3">
         <v>-300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-3400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-900</v>
-      </c>
-      <c r="W24" s="3">
-        <v>-400</v>
       </c>
       <c r="X24" s="3">
         <v>-400</v>
       </c>
       <c r="Y24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
       <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2062,168 +2111,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-18400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-147700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-6900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-38300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-12500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-8700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-20200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-8800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-7700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-18400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-147700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-38300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-12500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-20200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-7700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2302,8 +2360,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2382,8 +2443,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2462,8 +2526,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2542,17 +2609,20 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
@@ -2560,56 +2630,56 @@
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-1200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>800</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>300</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
@@ -2622,88 +2692,94 @@
       <c r="AB32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-18400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-147700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-38300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-12500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-20200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-8800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-7700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2782,173 +2858,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-18400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-147700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-38300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-12500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-20200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-8800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-7700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43100</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>42916</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>42735</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>42551</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2977,8 +3062,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3007,88 +3093,92 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>36600</v>
+      </c>
+      <c r="E41" s="3">
         <v>38600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>39200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>43400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>40800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>45900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>41800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>49100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>33600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>39500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>50300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>52100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>52200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>152700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>57500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>63800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3167,88 +3257,94 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E43" s="3">
         <v>11400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>13900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>13800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>13100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7400</v>
-      </c>
-      <c r="N43" s="3">
-        <v>12200</v>
       </c>
       <c r="O43" s="3">
         <v>12200</v>
       </c>
       <c r="P43" s="3">
+        <v>12200</v>
+      </c>
+      <c r="Q43" s="3">
         <v>8100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>9200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>12700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>9100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4800</v>
-      </c>
-      <c r="AA43" s="3">
-        <v>3500</v>
       </c>
       <c r="AB43" s="3">
         <v>3500</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3288,207 +3384,216 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q44" s="3">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R44" s="3">
         <v>400</v>
-      </c>
-      <c r="R44" s="3">
-        <v>800</v>
       </c>
       <c r="S44" s="3">
         <v>800</v>
       </c>
       <c r="T44" s="3">
+        <v>800</v>
+      </c>
+      <c r="U44" s="3">
         <v>900</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
-      </c>
       <c r="V44" s="3">
+        <v>0</v>
+      </c>
+      <c r="W44" s="3">
         <v>1200</v>
       </c>
-      <c r="W44" s="3">
-        <v>0</v>
-      </c>
-      <c r="X44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA44" s="3">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB44" s="3">
         <v>100</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E45" s="3">
         <v>6500</v>
-      </c>
-      <c r="E45" s="3">
-        <v>7400</v>
       </c>
       <c r="F45" s="3">
         <v>7400</v>
       </c>
       <c r="G45" s="3">
+        <v>7400</v>
+      </c>
+      <c r="H45" s="3">
         <v>8400</v>
-      </c>
-      <c r="H45" s="3">
-        <v>7900</v>
       </c>
       <c r="I45" s="3">
         <v>7900</v>
       </c>
       <c r="J45" s="3">
+        <v>7900</v>
+      </c>
+      <c r="K45" s="3">
         <v>7000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1100</v>
-      </c>
-      <c r="X45" s="3">
-        <v>1200</v>
       </c>
       <c r="Y45" s="3">
         <v>1200</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>5</v>
+      <c r="Z45" s="3">
+        <v>1200</v>
       </c>
       <c r="AA45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>52400</v>
+      </c>
+      <c r="E46" s="3">
         <v>56500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>55800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>60900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>63100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>67600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>62900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>67400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>49200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>54400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>62500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>68800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>70600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>163500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>70200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>72800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>18000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>18800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>17000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>13800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>9200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>8100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>9600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>8700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>8500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3528,14 +3633,14 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q47" s="3">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R47" s="3">
         <v>300</v>
-      </c>
-      <c r="R47" s="3">
-        <v>100</v>
       </c>
       <c r="S47" s="3">
         <v>100</v>
@@ -3543,8 +3648,8 @@
       <c r="T47" s="3">
         <v>100</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>5</v>
+      <c r="U47" s="3">
+        <v>100</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>5</v>
@@ -3552,8 +3657,8 @@
       <c r="W47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
@@ -3567,168 +3672,177 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E48" s="3">
         <v>8500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2100</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I48" s="3">
         <v>2900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2400</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M48" s="3">
         <v>3300</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P48" s="3">
+      <c r="P48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q48" s="3">
         <v>2100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E49" s="3">
         <v>20700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>23300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>26800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>29900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>31700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>162900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>174200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>191800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>196500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>200900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>206500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>204300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>7100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>10300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>6800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>7200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>7700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>7900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>7400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3807,8 +3921,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3887,8 +4004,11 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3896,43 +4016,43 @@
         <v>1700</v>
       </c>
       <c r="E52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F52" s="3">
         <v>5200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>13000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>500</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>100</v>
       </c>
       <c r="R52" s="3">
         <v>100</v>
@@ -3941,34 +4061,37 @@
         <v>100</v>
       </c>
       <c r="T52" s="3">
+        <v>100</v>
+      </c>
+      <c r="U52" s="3">
         <v>800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>200</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
-      </c>
       <c r="X52" s="3">
         <v>0</v>
       </c>
       <c r="Y52" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Z52" s="3">
         <v>200</v>
       </c>
       <c r="AA52" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="AB52" s="3">
         <v>800</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4047,88 +4170,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>81400</v>
+      </c>
+      <c r="E54" s="3">
         <v>87500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>88700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>95000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>96600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>103100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>230100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>246000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>250700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>260900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>276400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>283000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>278800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>173200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>78000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>79900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>24500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>26200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>23100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>22600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>15300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>15800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>17900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>17400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>17600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4157,8 +4286,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4187,88 +4317,92 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E57" s="3">
         <v>7000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6400</v>
-      </c>
-      <c r="I57" s="3">
-        <v>6300</v>
       </c>
       <c r="J57" s="3">
         <v>6300</v>
       </c>
       <c r="K57" s="3">
+        <v>6300</v>
+      </c>
+      <c r="L57" s="3">
         <v>5800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>13400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>9400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4305,38 +4439,38 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P58" s="3">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q58" s="3">
         <v>100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>300</v>
-      </c>
-      <c r="R58" s="3">
-        <v>500</v>
       </c>
       <c r="S58" s="3">
         <v>500</v>
       </c>
       <c r="T58" s="3">
+        <v>500</v>
+      </c>
+      <c r="U58" s="3">
         <v>900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>300</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="3" t="s">
-        <v>5</v>
+      <c r="Y58" s="3">
+        <v>0</v>
       </c>
       <c r="Z58" s="3" t="s">
         <v>5</v>
@@ -4347,195 +4481,204 @@
       <c r="AB58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E59" s="3">
         <v>29800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>27000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>27500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>25400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>26100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>20300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>21200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>24200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>27800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>28700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>24600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>21200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1300</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E60" s="3">
         <v>36700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>32500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>32300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>31000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>32500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>26700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>27400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>30000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>33000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>33300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>28800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>25500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>17300</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>15200</v>
       </c>
       <c r="R60" s="3">
         <v>15200</v>
       </c>
       <c r="S60" s="3">
+        <v>15200</v>
+      </c>
+      <c r="T60" s="3">
         <v>9100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>12300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>43300</v>
+      </c>
+      <c r="E61" s="3">
         <v>42200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>41100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>39800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>28500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>28200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>27900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>27700</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -4552,123 +4695,129 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="R61" s="3">
         <v>400</v>
       </c>
       <c r="S61" s="3">
+        <v>400</v>
+      </c>
+      <c r="T61" s="3">
         <v>500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2500</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E62" s="3">
         <v>13200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>12600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>21600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>23200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>21900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>400</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T62" s="3">
+      <c r="T62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U62" s="3">
         <v>700</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
-      </c>
-      <c r="V62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W62" s="3">
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X62" s="3">
         <v>300</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
-      </c>
       <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="3">
         <v>200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>300</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>400</v>
       </c>
       <c r="AB62" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4747,8 +4896,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4827,8 +4979,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4907,88 +5062,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>90300</v>
+      </c>
+      <c r="E66" s="3">
         <v>92100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>86600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>85000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>72000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>82300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>77700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>77000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>33700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>36900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>37200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>32500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>29400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>17700</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>15600</v>
       </c>
       <c r="R66" s="3">
         <v>15600</v>
       </c>
       <c r="S66" s="3">
+        <v>15600</v>
+      </c>
+      <c r="T66" s="3">
         <v>9600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>11000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>12900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>10600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>6500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5017,8 +5178,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5097,8 +5259,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5177,8 +5342,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5257,8 +5425,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5337,88 +5508,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-313500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-309300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-299900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-291800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-273400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-274900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-127200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-120200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-80900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-76400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-63800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-55100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-51400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-45800</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T72" s="3">
         <v>-21900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-23000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-16900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-25300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-14800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-14700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-13000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-10600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-8900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-6100</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5497,8 +5674,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5577,8 +5757,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5657,88 +5840,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E76" s="3">
         <v>-4600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>24600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>152400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>169000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>217000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>224000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>239200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>250400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>249400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>155600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>62400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>64300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>12000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>9300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>11100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5817,173 +6006,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43100</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>42916</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>42735</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>42551</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-18400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-147700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-38300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-12500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-20200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-8800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-7700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6012,88 +6210,92 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E83" s="3">
         <v>4400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4300</v>
-      </c>
-      <c r="F83" s="3">
-        <v>4200</v>
       </c>
       <c r="G83" s="3">
         <v>4200</v>
       </c>
       <c r="H83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I83" s="3">
         <v>6400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3200</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T83" s="3">
+      <c r="T83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U83" s="3">
         <v>4700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>6200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6172,8 +6374,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6252,8 +6457,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6332,8 +6540,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6412,8 +6623,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6492,88 +6706,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E89" s="3">
         <v>100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>7700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4600</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T89" s="3">
+      <c r="T89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U89" s="3">
         <v>6300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>5300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-200</v>
       </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
       <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6602,77 +6822,78 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1200</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-1800</v>
       </c>
       <c r="G91" s="3">
         <v>-1800</v>
       </c>
       <c r="H91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>1400</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T91" s="3">
-        <v>-200</v>
+      <c r="T91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U91" s="3">
         <v>-200</v>
       </c>
       <c r="V91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
@@ -6680,10 +6901,13 @@
         <v>0</v>
       </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6762,8 +6986,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6842,88 +7069,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1200</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-1800</v>
       </c>
       <c r="G94" s="3">
         <v>-1800</v>
       </c>
       <c r="H94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="I94" s="3">
         <v>-1600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8500</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-4000</v>
       </c>
       <c r="L94" s="3">
         <v>-4000</v>
       </c>
       <c r="M94" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-94600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1700</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T94" s="3">
+      <c r="T94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U94" s="3">
         <v>-2900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6952,8 +7185,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7032,8 +7266,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7112,8 +7349,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7192,8 +7432,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7272,244 +7515,256 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>1300</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>27000</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>500</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>-300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>154700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-400</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T100" s="3">
+      <c r="T100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U100" s="3">
         <v>200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>5700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>5200</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>2500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>3200</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>3400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>400</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T101" s="3">
+      <c r="T101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U101" s="3">
         <v>300</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-100</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
         <v>0</v>
       </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>300</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>4100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-7300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>15500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-10800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-100500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>142400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6400</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T102" s="3">
+      <c r="T102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U102" s="3">
         <v>3200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-4700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GAN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GAN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
   <si>
     <t>GAN</t>
   </si>
@@ -656,280 +656,287 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43100</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>42916</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>42735</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42551</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>30700</v>
+        <v>35600</v>
       </c>
       <c r="E8" s="3">
         <v>30700</v>
       </c>
       <c r="F8" s="3">
+        <v>30700</v>
+      </c>
+      <c r="G8" s="3">
         <v>29800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>33800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>35100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>36900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>32100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>35000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>37500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>30400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>32300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>34400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>27100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>35200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>30000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>14000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5000</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>4800</v>
       </c>
       <c r="AB8" s="3">
         <v>4800</v>
       </c>
       <c r="AC8" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AD8" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E9" s="3">
         <v>9300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>9400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>11700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>11500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>18500</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W9" s="3">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X9" s="3">
         <v>11900</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>5</v>
       </c>
@@ -945,74 +952,77 @@
       <c r="AC9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E10" s="3">
         <v>21400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>20900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>20600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>24300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>24900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>26900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>22700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>24500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>25800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>18900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>21500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>24000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>18400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>24700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>6400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>11500</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X10" s="3">
         <v>2100</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1028,8 +1038,11 @@
       <c r="AC10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1059,68 +1072,69 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E12" s="3">
         <v>9600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>9200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>11200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>9600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>7200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>9000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>7000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>4800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>11000</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U12" s="3">
+      <c r="U12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V12" s="3">
         <v>3400</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>5</v>
       </c>
@@ -1142,8 +1156,11 @@
       <c r="AC12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1225,55 +1242,58 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>900</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>8400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-9300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>137100</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>29600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3500</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>5</v>
@@ -1281,18 +1301,18 @@
       <c r="T14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3">
         <v>1700</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="3">
         <v>300</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1308,70 +1328,73 @@
       <c r="AC14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E15" s="3">
         <v>1800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4300</v>
-      </c>
-      <c r="G15" s="3">
-        <v>4200</v>
       </c>
       <c r="H15" s="3">
         <v>4200</v>
       </c>
       <c r="I15" s="3">
+        <v>4200</v>
+      </c>
+      <c r="J15" s="3">
         <v>6400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>6600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3300</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S15" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V15" s="3">
         <v>4300</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W15" s="3">
-        <v>0</v>
+      <c r="W15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X15" s="3">
         <v>0</v>
@@ -1391,8 +1414,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1419,174 +1445,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>33900</v>
+        <v>35300</v>
       </c>
       <c r="E17" s="3">
+        <v>34000</v>
+      </c>
+      <c r="F17" s="3">
         <v>40200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>37000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>50700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>31800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>182400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>37300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>72700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>41600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>46800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>39400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>37100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>32100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>54600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>14300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>16600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>27400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>22200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-3200</v>
+        <v>300</v>
       </c>
       <c r="E18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-9500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-7200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-16900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-145500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-37700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-16400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-19400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-4000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-8300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-8200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1616,20 +1649,21 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
@@ -1637,56 +1671,56 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>1200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-800</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-300</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
@@ -1699,123 +1733,129 @@
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-5200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-12700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-137900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-32000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-11800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-16300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-3900</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="3">
         <v>7000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E22" s="3">
         <v>1100</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3">
         <v>1300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1700</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K22" s="3">
         <v>1100</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1827,212 +1867,221 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>400</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V22" s="3">
         <v>200</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z22" s="3">
         <v>200</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="3" t="s">
-        <v>5</v>
+      <c r="AA22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>0</v>
       </c>
       <c r="AC22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-17800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-144300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-6600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-38600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-16000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-19900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-8600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-8600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-200</v>
+        <v>800</v>
       </c>
       <c r="E24" s="3">
         <v>-200</v>
       </c>
       <c r="F24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G24" s="3">
         <v>-300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-3400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-900</v>
-      </c>
-      <c r="X24" s="3">
-        <v>-400</v>
       </c>
       <c r="Y24" s="3">
         <v>-400</v>
       </c>
       <c r="Z24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
       <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2114,174 +2163,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-18400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-147700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-6900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-38300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-12500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-8700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-20200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-8800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-7700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-18400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-147700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-38300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-12500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-8700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-20200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-8800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-7700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2363,8 +2421,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2446,8 +2507,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2529,8 +2593,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2612,20 +2679,23 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
@@ -2633,56 +2703,56 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-1200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>800</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>300</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
@@ -2695,91 +2765,97 @@
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-18400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-147700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-38300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-12500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-8700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-20200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-8800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-7700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2861,179 +2937,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-18400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-147700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-38300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-12500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-8700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-20200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-8800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-7700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43100</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>42916</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>42735</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42551</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3063,8 +3148,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3094,91 +3180,95 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>36900</v>
+      </c>
+      <c r="E41" s="3">
         <v>36600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>38600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>39200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>43400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>40800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>45900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>41800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>49100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>33600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>39500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>50300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>52100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>52200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>152700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>57500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>63800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3260,91 +3350,97 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E43" s="3">
         <v>9400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>11400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>13900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>13800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>13100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>11200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7400</v>
-      </c>
-      <c r="O43" s="3">
-        <v>12200</v>
       </c>
       <c r="P43" s="3">
         <v>12200</v>
       </c>
       <c r="Q43" s="3">
+        <v>12200</v>
+      </c>
+      <c r="R43" s="3">
         <v>8100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>9100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>9200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>12700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>9100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4800</v>
-      </c>
-      <c r="AB43" s="3">
-        <v>3500</v>
       </c>
       <c r="AC43" s="3">
         <v>3500</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3387,213 +3483,222 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R44" s="3">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S44" s="3">
         <v>400</v>
-      </c>
-      <c r="S44" s="3">
-        <v>800</v>
       </c>
       <c r="T44" s="3">
         <v>800</v>
       </c>
       <c r="U44" s="3">
+        <v>800</v>
+      </c>
+      <c r="V44" s="3">
         <v>900</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
-      </c>
       <c r="W44" s="3">
+        <v>0</v>
+      </c>
+      <c r="X44" s="3">
         <v>1200</v>
       </c>
-      <c r="X44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z44" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB44" s="3">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC44" s="3">
         <v>100</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E45" s="3">
         <v>6400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6500</v>
-      </c>
-      <c r="F45" s="3">
-        <v>7400</v>
       </c>
       <c r="G45" s="3">
         <v>7400</v>
       </c>
       <c r="H45" s="3">
+        <v>7400</v>
+      </c>
+      <c r="I45" s="3">
         <v>8400</v>
-      </c>
-      <c r="I45" s="3">
-        <v>7900</v>
       </c>
       <c r="J45" s="3">
         <v>7900</v>
       </c>
       <c r="K45" s="3">
+        <v>7900</v>
+      </c>
+      <c r="L45" s="3">
         <v>7000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1100</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>1200</v>
       </c>
       <c r="Z45" s="3">
         <v>1200</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>5</v>
+      <c r="AA45" s="3">
+        <v>1200</v>
       </c>
       <c r="AB45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>53900</v>
+      </c>
+      <c r="E46" s="3">
         <v>52400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>56500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>55800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>60900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>63100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>67600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>62900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>67400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>49200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>54400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>62500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>68800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>70600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>163500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>70200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>72800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>18000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>18800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>17000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>13800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>9200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>8100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>9600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>8700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>8500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3636,14 +3741,14 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R47" s="3">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S47" s="3">
         <v>300</v>
-      </c>
-      <c r="S47" s="3">
-        <v>100</v>
       </c>
       <c r="T47" s="3">
         <v>100</v>
@@ -3651,8 +3756,8 @@
       <c r="U47" s="3">
         <v>100</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>5</v>
+      <c r="V47" s="3">
+        <v>100</v>
       </c>
       <c r="W47" s="3" t="s">
         <v>5</v>
@@ -3660,8 +3765,8 @@
       <c r="X47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
@@ -3675,174 +3780,183 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E48" s="3">
         <v>7800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2100</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="3">
         <v>2900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2400</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N48" s="3">
         <v>3300</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R48" s="3">
         <v>2100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E49" s="3">
         <v>19600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>20700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>23300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>26800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>29900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>31700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>162900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>174200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>191800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>196500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>200900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>206500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>204300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>7100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>10300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>6800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>7200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>7700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>7900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3924,8 +4038,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4007,8 +4124,11 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4019,43 +4139,43 @@
         <v>1700</v>
       </c>
       <c r="F52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G52" s="3">
         <v>5200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>13000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>500</v>
-      </c>
-      <c r="R52" s="3">
-        <v>100</v>
       </c>
       <c r="S52" s="3">
         <v>100</v>
@@ -4064,34 +4184,37 @@
         <v>100</v>
       </c>
       <c r="U52" s="3">
+        <v>100</v>
+      </c>
+      <c r="V52" s="3">
         <v>800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>200</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
-      </c>
       <c r="Y52" s="3">
         <v>0</v>
       </c>
       <c r="Z52" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AA52" s="3">
         <v>200</v>
       </c>
       <c r="AB52" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="AC52" s="3">
         <v>800</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4173,91 +4296,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>81200</v>
+      </c>
+      <c r="E54" s="3">
         <v>81400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>87500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>88700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>95000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>96600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>103100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>230100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>246000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>250700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>260900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>276400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>283000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>278800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>173200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>78000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>79900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>24500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>26200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>23100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>22600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>15300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>15800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>17900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>17400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>17600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4287,8 +4416,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4318,91 +4448,95 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E57" s="3">
         <v>6700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6400</v>
-      </c>
-      <c r="J57" s="3">
-        <v>6300</v>
       </c>
       <c r="K57" s="3">
         <v>6300</v>
       </c>
       <c r="L57" s="3">
+        <v>6300</v>
+      </c>
+      <c r="M57" s="3">
         <v>5800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>13400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>12900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>9400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>9100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>4200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4442,38 +4576,38 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q58" s="3">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R58" s="3">
         <v>100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>300</v>
-      </c>
-      <c r="S58" s="3">
-        <v>500</v>
       </c>
       <c r="T58" s="3">
         <v>500</v>
       </c>
       <c r="U58" s="3">
+        <v>500</v>
+      </c>
+      <c r="V58" s="3">
         <v>900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>300</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="3" t="s">
-        <v>5</v>
+      <c r="Z58" s="3">
+        <v>0</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>5</v>
@@ -4484,204 +4618,213 @@
       <c r="AC58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E59" s="3">
         <v>26500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>29800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>27000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>27500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>25400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>26100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>20300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>21200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>24200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>27800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>28700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>24600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>21200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>7100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1300</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AC59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>34600</v>
+      </c>
+      <c r="E60" s="3">
         <v>33200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>36700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>32500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>32300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>31000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>32500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>26700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>27400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>30000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>33000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>33300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>28800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>25500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>17300</v>
-      </c>
-      <c r="R60" s="3">
-        <v>15200</v>
       </c>
       <c r="S60" s="3">
         <v>15200</v>
       </c>
       <c r="T60" s="3">
+        <v>15200</v>
+      </c>
+      <c r="U60" s="3">
         <v>9100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>12300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>44500</v>
+      </c>
+      <c r="E61" s="3">
         <v>43300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>42200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>41100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>39800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>28500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>28200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>27900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>27700</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4698,126 +4841,132 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="S61" s="3">
         <v>400</v>
       </c>
       <c r="T61" s="3">
+        <v>400</v>
+      </c>
+      <c r="U61" s="3">
         <v>500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2500</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E62" s="3">
         <v>13800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>12600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>21600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>23200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>21900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>400</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U62" s="3">
+      <c r="U62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V62" s="3">
         <v>700</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
-      </c>
-      <c r="W62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X62" s="3">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y62" s="3">
         <v>300</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
-      </c>
       <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="3">
         <v>200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>300</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>400</v>
       </c>
       <c r="AC62" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4899,8 +5048,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4982,8 +5134,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5065,91 +5220,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>91300</v>
+      </c>
+      <c r="E66" s="3">
         <v>90300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>92100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>86600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>85000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>72000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>82300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>77700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>77000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>33700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>36900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>37200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>32500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>29400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>17700</v>
-      </c>
-      <c r="R66" s="3">
-        <v>15600</v>
       </c>
       <c r="S66" s="3">
         <v>15600</v>
       </c>
       <c r="T66" s="3">
+        <v>15600</v>
+      </c>
+      <c r="U66" s="3">
         <v>9600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>12900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>10600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5179,8 +5340,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5262,8 +5424,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5345,8 +5510,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5428,8 +5596,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5511,91 +5682,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-315200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-313500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-309300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-299900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-291800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-273400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-274900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-127200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-120200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-80900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-76400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-63800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-55100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-51400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-45800</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U72" s="3">
         <v>-21900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-23000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-16900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-25300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-14800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-14700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-13000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-10600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-8900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-6100</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5677,8 +5854,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5760,8 +5940,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5843,91 +6026,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E76" s="3">
         <v>-8900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-4600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>24600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>20800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>152400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>169000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>217000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>224000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>239200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>250400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>249400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>155600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>62400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>64300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>14800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>10200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>11100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6009,179 +6198,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43100</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>42916</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>42735</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42551</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-18400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-147700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-38300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-12500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-8700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-20200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-8800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-7700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6211,91 +6409,95 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E83" s="3">
         <v>1800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4300</v>
-      </c>
-      <c r="G83" s="3">
-        <v>4200</v>
       </c>
       <c r="H83" s="3">
         <v>4200</v>
       </c>
       <c r="I83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="J83" s="3">
         <v>6400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>3200</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V83" s="3">
         <v>4700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>6200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>2000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6377,8 +6579,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6460,8 +6665,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6543,8 +6751,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6626,8 +6837,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6709,91 +6923,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-6400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-6300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4600</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V89" s="3">
         <v>6300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>5300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-200</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
-      </c>
       <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6823,80 +7043,81 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1200</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-1800</v>
       </c>
       <c r="H91" s="3">
         <v>-1800</v>
       </c>
       <c r="I91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="J91" s="3">
         <v>-1100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>1400</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U91" s="3">
-        <v>-200</v>
+      <c r="U91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V91" s="3">
         <v>-200</v>
       </c>
       <c r="W91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
       <c r="AA91" s="3">
         <v>0</v>
       </c>
@@ -6904,10 +7125,13 @@
         <v>0</v>
       </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6989,8 +7213,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7072,91 +7299,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1200</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-1800</v>
       </c>
       <c r="H94" s="3">
         <v>-1800</v>
       </c>
       <c r="I94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="J94" s="3">
         <v>-1600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8500</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-4000</v>
       </c>
       <c r="M94" s="3">
         <v>-4000</v>
       </c>
       <c r="N94" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-7900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-94600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1700</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V94" s="3">
         <v>-2900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7186,8 +7419,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7269,8 +7503,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7352,8 +7589,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7435,8 +7675,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7518,8 +7761,11 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7527,244 +7773,253 @@
         <v>0</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>1300</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>27000</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>500</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>154700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-400</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V100" s="3">
         <v>200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>5700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>5200</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>2500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>3200</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>3400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>400</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U101" s="3">
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V101" s="3">
         <v>300</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-100</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
         <v>0</v>
       </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>300</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-7300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>15500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-10800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-100500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>142400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-6400</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3">
         <v>3200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-4700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GAN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GAN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
   <si>
     <t>GAN</t>
   </si>
@@ -656,290 +656,297 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>42916</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42735</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42551</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>37100</v>
+      </c>
+      <c r="E8" s="3">
         <v>35600</v>
-      </c>
-      <c r="E8" s="3">
-        <v>30700</v>
       </c>
       <c r="F8" s="3">
         <v>30700</v>
       </c>
       <c r="G8" s="3">
+        <v>30700</v>
+      </c>
+      <c r="H8" s="3">
         <v>29800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>33800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>35100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>36900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>32100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>35000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>37500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>30400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>32300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>34400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>27100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>35200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>30000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>11300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>14000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5000</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>4800</v>
       </c>
       <c r="AC8" s="3">
         <v>4800</v>
       </c>
       <c r="AD8" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AE8" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E9" s="3">
         <v>10200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>9500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>11700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>11500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>18500</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X9" s="3">
+      <c r="X9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y9" s="3">
         <v>11900</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>5</v>
       </c>
@@ -955,77 +962,80 @@
       <c r="AD9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>25400</v>
+        <v>27200</v>
       </c>
       <c r="E10" s="3">
-        <v>21400</v>
+        <v>25300</v>
       </c>
       <c r="F10" s="3">
+        <v>21300</v>
+      </c>
+      <c r="G10" s="3">
         <v>20900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>20600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>24300</v>
       </c>
-      <c r="I10" s="3">
-        <v>24900</v>
-      </c>
       <c r="J10" s="3">
+        <v>25000</v>
+      </c>
+      <c r="K10" s="3">
         <v>26900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>22700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>24500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>25800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>18900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>21500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>24000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>18400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>24700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>6400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>11500</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="X10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y10" s="3">
         <v>2100</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1041,8 +1051,11 @@
       <c r="AD10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1073,71 +1086,72 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E12" s="3">
         <v>8100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>9600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>8300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>9200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>11200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>9600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>7200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>9000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>7000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>4800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>11000</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V12" s="3">
+      <c r="V12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W12" s="3">
         <v>3400</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>5</v>
       </c>
@@ -1159,8 +1173,11 @@
       <c r="AD12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1245,8 +1262,11 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1256,47 +1276,47 @@
       <c r="E14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3">
         <v>900</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>8400</v>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I14" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="J14" s="3">
         <v>-9300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>137100</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>29600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3500</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>5</v>
@@ -1304,18 +1324,18 @@
       <c r="U14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W14" s="3">
         <v>1700</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y14" s="3">
         <v>300</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1331,73 +1351,76 @@
       <c r="AD14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4300</v>
-      </c>
-      <c r="H15" s="3">
-        <v>4200</v>
       </c>
       <c r="I15" s="3">
         <v>4200</v>
       </c>
       <c r="J15" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K15" s="3">
         <v>6400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>6600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>4400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3300</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T15" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V15" s="3">
+      <c r="V15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W15" s="3">
         <v>4300</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X15" s="3">
-        <v>0</v>
+      <c r="X15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y15" s="3">
         <v>0</v>
@@ -1417,8 +1440,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1446,180 +1472,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E17" s="3">
         <v>35300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>34000</v>
       </c>
-      <c r="F17" s="3">
-        <v>40200</v>
-      </c>
       <c r="G17" s="3">
+        <v>39300</v>
+      </c>
+      <c r="H17" s="3">
         <v>37000</v>
       </c>
-      <c r="H17" s="3">
-        <v>50700</v>
-      </c>
       <c r="I17" s="3">
-        <v>31800</v>
+        <v>42300</v>
       </c>
       <c r="J17" s="3">
+        <v>41100</v>
+      </c>
+      <c r="K17" s="3">
         <v>182400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>37300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>72700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>41600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>46800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>39400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>37100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>32100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>54600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>14300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>16600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>27400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>22200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>7700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>300</v>
+        <v>2100</v>
       </c>
       <c r="E18" s="3">
+        <v>200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3300</v>
       </c>
-      <c r="F18" s="3">
-        <v>-9500</v>
-      </c>
       <c r="G18" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="H18" s="3">
         <v>-7200</v>
       </c>
-      <c r="H18" s="3">
-        <v>-16900</v>
-      </c>
       <c r="I18" s="3">
-        <v>3300</v>
+        <v>-8600</v>
       </c>
       <c r="J18" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="K18" s="3">
         <v>-145500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-37700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-16400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-7100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-19400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-4000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-8300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1650,80 +1683,81 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>4000</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3">
+        <v>16700</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>400</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>1200</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="U20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3">
-        <v>-800</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>400</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="W20" s="3">
+        <v>100</v>
+      </c>
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="Y20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-300</v>
       </c>
-      <c r="U20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="V20" s="3">
-        <v>100</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-300</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
@@ -1736,94 +1770,100 @@
       <c r="AD20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E21" s="3">
         <v>2100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1400</v>
       </c>
-      <c r="F21" s="3">
-        <v>-5200</v>
-      </c>
       <c r="G21" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="H21" s="3">
         <v>-2800</v>
       </c>
-      <c r="H21" s="3">
-        <v>-12700</v>
-      </c>
       <c r="I21" s="3">
-        <v>7500</v>
+        <v>-21000</v>
       </c>
       <c r="J21" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="K21" s="3">
         <v>-137900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-32000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-11800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-16300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-3900</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W21" s="3">
         <v>7000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1831,34 +1871,34 @@
         <v>1200</v>
       </c>
       <c r="E22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F22" s="3">
         <v>1100</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G22" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="H22" s="3">
         <v>1300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1700</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L22" s="3">
         <v>1100</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1870,218 +1910,227 @@
         <v>0</v>
       </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>400</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W22" s="3">
         <v>200</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="Z22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA22" s="3">
         <v>200</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="3" t="s">
-        <v>5</v>
+      <c r="AB22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>0</v>
       </c>
       <c r="AD22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-17800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-144300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-6600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-38600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-16000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-19900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-8600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-8600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E24" s="3">
         <v>800</v>
-      </c>
-      <c r="E24" s="3">
-        <v>-200</v>
       </c>
       <c r="F24" s="3">
         <v>-200</v>
       </c>
       <c r="G24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H24" s="3">
         <v>-300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-3400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-900</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>-400</v>
       </c>
       <c r="Z24" s="3">
         <v>-400</v>
       </c>
       <c r="AA24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AB24" s="3">
         <v>-500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
       <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2166,180 +2215,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-8200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-18400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-147700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-6900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-38300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-12500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-8700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-20200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-8800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-8200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-18400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-147700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-38300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-12500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-8700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-20200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-8800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2424,8 +2482,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2510,8 +2571,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2596,8 +2660,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2682,80 +2749,83 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="L32" s="3">
+        <v>300</v>
+      </c>
+      <c r="M32" s="3">
+        <v>800</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="U32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3">
-        <v>800</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="W32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="Y32" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z32" s="3">
         <v>300</v>
       </c>
-      <c r="U32" s="3">
-        <v>100</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="W32" s="3">
-        <v>100</v>
-      </c>
-      <c r="X32" s="3">
-        <v>400</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>300</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
@@ -2768,94 +2838,100 @@
       <c r="AD32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-8200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-18400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-147700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-38300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-12500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-8700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-20200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-8800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2940,185 +3016,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-8200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-18400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-147700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-38300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-12500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-8700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-20200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-8800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>42916</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42735</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42551</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3149,8 +3234,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3181,94 +3267,98 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>36500</v>
+      </c>
+      <c r="E41" s="3">
         <v>36900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>36600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>38600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>39200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>43400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>40800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>45900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>41800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>49100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>33600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>39500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>50300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>52100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>52200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>152700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>57500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>63800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3353,117 +3443,123 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E43" s="3">
         <v>8800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>13900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>13800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>13100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>11200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7400</v>
-      </c>
-      <c r="P43" s="3">
-        <v>12200</v>
       </c>
       <c r="Q43" s="3">
         <v>12200</v>
       </c>
       <c r="R43" s="3">
+        <v>12200</v>
+      </c>
+      <c r="S43" s="3">
         <v>8100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>9100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>9200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>12700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>9100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>4300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4800</v>
-      </c>
-      <c r="AC43" s="3">
-        <v>3500</v>
       </c>
       <c r="AD43" s="3">
         <v>3500</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3486,242 +3582,251 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S44" s="3">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T44" s="3">
         <v>400</v>
-      </c>
-      <c r="T44" s="3">
-        <v>800</v>
       </c>
       <c r="U44" s="3">
         <v>800</v>
       </c>
       <c r="V44" s="3">
+        <v>800</v>
+      </c>
+      <c r="W44" s="3">
         <v>900</v>
       </c>
-      <c r="W44" s="3">
-        <v>0</v>
-      </c>
       <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
         <v>1200</v>
       </c>
-      <c r="Y44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA44" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC44" s="3">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD44" s="3">
         <v>100</v>
       </c>
-      <c r="AD44" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>8100</v>
+        <v>4200</v>
       </c>
       <c r="E45" s="3">
-        <v>6400</v>
+        <v>4500</v>
       </c>
       <c r="F45" s="3">
-        <v>6500</v>
+        <v>2500</v>
       </c>
       <c r="G45" s="3">
-        <v>7400</v>
+        <v>3200</v>
       </c>
       <c r="H45" s="3">
-        <v>7400</v>
+        <v>4100</v>
       </c>
       <c r="I45" s="3">
-        <v>8400</v>
+        <v>3500</v>
       </c>
       <c r="J45" s="3">
-        <v>7900</v>
+        <v>3100</v>
       </c>
       <c r="K45" s="3">
         <v>7900</v>
       </c>
       <c r="L45" s="3">
+        <v>7900</v>
+      </c>
+      <c r="M45" s="3">
         <v>7000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1100</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>1200</v>
       </c>
       <c r="AA45" s="3">
         <v>1200</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>5</v>
+      <c r="AB45" s="3">
+        <v>1200</v>
       </c>
       <c r="AC45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>55500</v>
+      </c>
+      <c r="E46" s="3">
         <v>53900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>52400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>56500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>55800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>60900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>63100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>67600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>62900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>67400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>49200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>54400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>62500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>68800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>70600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>163500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>70200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>72800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>18000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>18800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>17000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>13800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>9200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>8100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>9600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>8700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>8500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3744,14 +3849,14 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S47" s="3">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T47" s="3">
         <v>300</v>
-      </c>
-      <c r="T47" s="3">
-        <v>100</v>
       </c>
       <c r="U47" s="3">
         <v>100</v>
@@ -3759,8 +3864,8 @@
       <c r="V47" s="3">
         <v>100</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>5</v>
+      <c r="W47" s="3">
+        <v>100</v>
       </c>
       <c r="X47" s="3" t="s">
         <v>5</v>
@@ -3768,8 +3873,8 @@
       <c r="Y47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
@@ -3783,180 +3888,189 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E48" s="3">
         <v>7300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8500</v>
       </c>
-      <c r="G48" s="3">
-        <v>4400</v>
-      </c>
       <c r="H48" s="3">
+        <v>7500</v>
+      </c>
+      <c r="I48" s="3">
+        <v>5300</v>
+      </c>
+      <c r="J48" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K48" s="3">
+        <v>2900</v>
+      </c>
+      <c r="L48" s="3">
+        <v>2500</v>
+      </c>
+      <c r="M48" s="3">
+        <v>2400</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S48" s="3">
         <v>2100</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J48" s="3">
-        <v>2900</v>
-      </c>
-      <c r="K48" s="3">
-        <v>2500</v>
-      </c>
-      <c r="L48" s="3">
-        <v>2400</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N48" s="3">
-        <v>3300</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R48" s="3">
-        <v>2100</v>
-      </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E49" s="3">
         <v>18400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>19600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>20700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>23300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>26800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>29900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>31700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>162900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>174200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>191800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>196500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>200900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>206500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>204300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>7100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>10300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>6800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>7200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>7700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>7400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4041,8 +4155,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4127,8 +4244,11 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4142,43 +4262,43 @@
         <v>1700</v>
       </c>
       <c r="G52" s="3">
-        <v>5200</v>
+        <v>400</v>
       </c>
       <c r="H52" s="3">
-        <v>5100</v>
+        <v>2200</v>
       </c>
       <c r="I52" s="3">
-        <v>3600</v>
+        <v>1900</v>
       </c>
       <c r="J52" s="3">
         <v>900</v>
       </c>
       <c r="K52" s="3">
+        <v>900</v>
+      </c>
+      <c r="L52" s="3">
         <v>1800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>13000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>500</v>
-      </c>
-      <c r="S52" s="3">
-        <v>100</v>
       </c>
       <c r="T52" s="3">
         <v>100</v>
@@ -4187,34 +4307,37 @@
         <v>100</v>
       </c>
       <c r="V52" s="3">
+        <v>100</v>
+      </c>
+      <c r="W52" s="3">
         <v>800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>200</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
-      </c>
       <c r="Z52" s="3">
         <v>0</v>
       </c>
       <c r="AA52" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AB52" s="3">
         <v>200</v>
       </c>
       <c r="AC52" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="AD52" s="3">
         <v>800</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4299,94 +4422,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>82600</v>
+      </c>
+      <c r="E54" s="3">
         <v>81200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>81400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>87500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>88700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>95000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>96600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>103100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>230100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>246000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>250700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>260900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>276400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>283000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>278800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>173200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>78000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>79900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>24500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>26200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>23100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>22600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>15300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>15800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>17900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>17400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>17600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4417,8 +4546,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4449,114 +4579,118 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E57" s="3">
         <v>6300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6400</v>
-      </c>
-      <c r="K57" s="3">
-        <v>6300</v>
       </c>
       <c r="L57" s="3">
         <v>6300</v>
       </c>
       <c r="M57" s="3">
+        <v>6300</v>
+      </c>
+      <c r="N57" s="3">
         <v>5800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>13400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>12900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -4579,38 +4713,38 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R58" s="3">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S58" s="3">
         <v>100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>300</v>
-      </c>
-      <c r="T58" s="3">
-        <v>500</v>
       </c>
       <c r="U58" s="3">
         <v>500</v>
       </c>
       <c r="V58" s="3">
+        <v>500</v>
+      </c>
+      <c r="W58" s="3">
         <v>900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>300</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA58" s="3" t="s">
-        <v>5</v>
+      <c r="AA58" s="3">
+        <v>0</v>
       </c>
       <c r="AB58" s="3" t="s">
         <v>5</v>
@@ -4621,213 +4755,222 @@
       <c r="AD58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>28400</v>
+        <v>14600</v>
       </c>
       <c r="E59" s="3">
-        <v>26500</v>
+        <v>18400</v>
       </c>
       <c r="F59" s="3">
-        <v>29800</v>
+        <v>16500</v>
       </c>
       <c r="G59" s="3">
-        <v>27000</v>
+        <v>17100</v>
       </c>
       <c r="H59" s="3">
-        <v>27500</v>
+        <v>15100</v>
       </c>
       <c r="I59" s="3">
-        <v>25400</v>
+        <v>14000</v>
       </c>
       <c r="J59" s="3">
+        <v>14800</v>
+      </c>
+      <c r="K59" s="3">
         <v>26100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>20300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>21200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>24200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>27800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>28700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>24600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>21200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>12600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>7100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1300</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AD59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E60" s="3">
         <v>34600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>33200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>36700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>32500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>32300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>31000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>32500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>26700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>27400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>30000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>33000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>33300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>28800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>25500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>17300</v>
-      </c>
-      <c r="S60" s="3">
-        <v>15200</v>
       </c>
       <c r="T60" s="3">
         <v>15200</v>
       </c>
       <c r="U60" s="3">
+        <v>15200</v>
+      </c>
+      <c r="V60" s="3">
         <v>9100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>12300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>44500</v>
+        <v>48700</v>
       </c>
       <c r="E61" s="3">
-        <v>43300</v>
+        <v>47500</v>
       </c>
       <c r="F61" s="3">
-        <v>42200</v>
+        <v>46600</v>
       </c>
       <c r="G61" s="3">
-        <v>41100</v>
+        <v>45800</v>
       </c>
       <c r="H61" s="3">
-        <v>39800</v>
+        <v>44800</v>
       </c>
       <c r="I61" s="3">
+        <v>41500</v>
+      </c>
+      <c r="J61" s="3">
         <v>28500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>28200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>27900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>27700</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -4844,129 +4987,135 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T61" s="3">
         <v>400</v>
       </c>
       <c r="U61" s="3">
+        <v>400</v>
+      </c>
+      <c r="V61" s="3">
         <v>500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2500</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>12200</v>
+        <v>1900</v>
       </c>
       <c r="E62" s="3">
-        <v>13800</v>
+        <v>1700</v>
       </c>
       <c r="F62" s="3">
-        <v>13200</v>
+        <v>1500</v>
       </c>
       <c r="G62" s="3">
-        <v>13100</v>
+        <v>1400</v>
       </c>
       <c r="H62" s="3">
-        <v>13000</v>
+        <v>4700</v>
       </c>
       <c r="I62" s="3">
-        <v>12600</v>
+        <v>5800</v>
       </c>
       <c r="J62" s="3">
+        <v>7400</v>
+      </c>
+      <c r="K62" s="3">
         <v>21600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>23200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>21900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>400</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V62" s="3">
+      <c r="V62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W62" s="3">
         <v>700</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y62" s="3">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z62" s="3">
         <v>300</v>
       </c>
-      <c r="Z62" s="3">
-        <v>0</v>
-      </c>
       <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="3">
         <v>200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>300</v>
-      </c>
-      <c r="AC62" s="3">
-        <v>400</v>
       </c>
       <c r="AD62" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5051,8 +5200,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5137,8 +5289,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5223,94 +5378,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>88400</v>
+      </c>
+      <c r="E66" s="3">
         <v>91300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>90300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>92100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>86600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>85000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>72000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>82300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>77700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>77000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>33700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>36900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>37200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>32500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>29400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>17700</v>
-      </c>
-      <c r="S66" s="3">
-        <v>15600</v>
       </c>
       <c r="T66" s="3">
         <v>15600</v>
       </c>
       <c r="U66" s="3">
+        <v>15600</v>
+      </c>
+      <c r="V66" s="3">
         <v>9600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>11000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>12900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>10600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5341,8 +5502,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5427,8 +5589,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5513,8 +5678,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5599,8 +5767,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5685,94 +5856,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-313100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-315200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-313500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-309300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-299900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-291800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-273400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-274900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-127200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-120200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-80900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-76400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-63800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-55100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-51400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-45800</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V72" s="3">
         <v>-21900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-23000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-16900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-25300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-14800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-14700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-10600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-8900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-6100</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5857,8 +6034,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5943,8 +6123,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6029,94 +6212,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-10200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-8900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-4600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>24600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>20800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>152400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>169000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>217000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>224000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>239200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>250400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>249400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>155600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>62400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>64300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>14800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>10200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>11100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>13500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6201,185 +6390,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>42916</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42735</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42551</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-8200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-18400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-147700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-38300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-12500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-8700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-20200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-8800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6410,94 +6608,98 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1900</v>
+        <v>500</v>
       </c>
       <c r="E83" s="3">
-        <v>1800</v>
+        <v>400</v>
       </c>
       <c r="F83" s="3">
+        <v>400</v>
+      </c>
+      <c r="G83" s="3">
+        <v>500</v>
+      </c>
+      <c r="H83" s="3">
+        <v>300</v>
+      </c>
+      <c r="I83" s="3">
+        <v>400</v>
+      </c>
+      <c r="J83" s="3">
+        <v>300</v>
+      </c>
+      <c r="K83" s="3">
+        <v>6400</v>
+      </c>
+      <c r="L83" s="3">
+        <v>5900</v>
+      </c>
+      <c r="M83" s="3">
+        <v>6600</v>
+      </c>
+      <c r="N83" s="3">
         <v>4400</v>
       </c>
-      <c r="G83" s="3">
-        <v>4300</v>
-      </c>
-      <c r="H83" s="3">
-        <v>4200</v>
-      </c>
-      <c r="I83" s="3">
-        <v>4200</v>
-      </c>
-      <c r="J83" s="3">
-        <v>6400</v>
-      </c>
-      <c r="K83" s="3">
-        <v>5900</v>
-      </c>
-      <c r="L83" s="3">
-        <v>6600</v>
-      </c>
-      <c r="M83" s="3">
-        <v>4400</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3200</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V83" s="3">
+      <c r="V83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W83" s="3">
         <v>4700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>6200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>2400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>2000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6582,8 +6784,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6668,8 +6873,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6754,8 +6962,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6840,8 +7051,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6926,94 +7140,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E89" s="3">
         <v>1200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-6400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-6300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4600</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V89" s="3">
+      <c r="V89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W89" s="3">
         <v>6300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>5300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-200</v>
       </c>
-      <c r="AB89" s="3">
-        <v>0</v>
-      </c>
       <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7044,83 +7264,84 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-600</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>-700</v>
+        <v>-200</v>
       </c>
       <c r="F91" s="3">
-        <v>-2000</v>
+        <v>-100</v>
       </c>
       <c r="G91" s="3">
-        <v>-1200</v>
+        <v>-1500</v>
       </c>
       <c r="H91" s="3">
-        <v>-1800</v>
+        <v>-300</v>
       </c>
       <c r="I91" s="3">
-        <v>-1800</v>
+        <v>-1000</v>
       </c>
       <c r="J91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>1400</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V91" s="3">
-        <v>-200</v>
+      <c r="V91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W91" s="3">
         <v>-200</v>
       </c>
       <c r="X91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
       <c r="AB91" s="3">
         <v>0</v>
       </c>
@@ -7128,10 +7349,13 @@
         <v>0</v>
       </c>
       <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7216,8 +7440,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7302,94 +7529,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1200</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-1800</v>
       </c>
       <c r="I94" s="3">
         <v>-1800</v>
       </c>
       <c r="J94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8500</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-4000</v>
       </c>
       <c r="N94" s="3">
         <v>-4000</v>
       </c>
       <c r="O94" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-94600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1700</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V94" s="3">
+      <c r="V94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W94" s="3">
         <v>-2900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7420,31 +7653,32 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7506,8 +7740,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7592,8 +7829,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7678,8 +7918,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7764,8 +8007,11 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7776,250 +8022,259 @@
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>1300</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>27000</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>500</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>-300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>154700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-400</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V100" s="3">
+      <c r="V100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W100" s="3">
         <v>200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>5700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>5200</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>2500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>3200</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-300</v>
+        <v>-700</v>
       </c>
       <c r="E101" s="3">
+        <v>300</v>
+      </c>
+      <c r="F101" s="3">
+        <v>800</v>
+      </c>
+      <c r="G101" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="J101" s="3">
+        <v>100</v>
+      </c>
+      <c r="K101" s="3">
+        <v>3400</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="N101" s="3">
+        <v>100</v>
+      </c>
+      <c r="O101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="P101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>200</v>
+      </c>
+      <c r="R101" s="3">
         <v>-1000</v>
       </c>
-      <c r="F101" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-700</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="S101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T101" s="3">
+        <v>400</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3">
-        <v>800</v>
-      </c>
-      <c r="J101" s="3">
-        <v>3400</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-800</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
-        <v>-500</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-400</v>
-      </c>
-      <c r="P101" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="R101" s="3">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
-        <v>400</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V101" s="3">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>300</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
-      <c r="X101" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>300</v>
-      </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E102" s="3">
         <v>300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>4100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-7300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>15500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-10800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-100500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>142400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6400</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V102" s="3">
+      <c r="V102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W102" s="3">
         <v>3200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-4700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GAN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GAN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
   <si>
     <t>GAN</t>
   </si>
@@ -656,300 +656,306 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42735</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42551</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E8" s="3">
         <v>37100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>35600</v>
-      </c>
-      <c r="F8" s="3">
-        <v>30700</v>
       </c>
       <c r="G8" s="3">
         <v>30700</v>
       </c>
       <c r="H8" s="3">
+        <v>30700</v>
+      </c>
+      <c r="I8" s="3">
         <v>29800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>33800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>35100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>36900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>32100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>35000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>37500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>30400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>32300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>34400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>27100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>35200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>30000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>11300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>14000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5000</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>4800</v>
       </c>
       <c r="AD8" s="3">
         <v>4800</v>
       </c>
       <c r="AE8" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AF8" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E9" s="3">
         <v>9900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>9200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>9500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>10200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>11700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>11500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>10500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>18500</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y9" s="3">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z9" s="3">
         <v>11900</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA9" s="3" t="s">
         <v>5</v>
       </c>
@@ -965,80 +971,83 @@
       <c r="AE9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E10" s="3">
         <v>27200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>25300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>21300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>20900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>20600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>24300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>25000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>26900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>22700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>24500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>25800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>18900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>21500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>24000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>18400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>24700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>6400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>11500</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z10" s="3">
         <v>2100</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1054,8 +1063,11 @@
       <c r="AE10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1087,74 +1099,75 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E12" s="3">
         <v>8500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>9600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>8300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>9200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>11200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>9600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>7200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>9000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>7000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>4800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>5200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>11000</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W12" s="3">
+      <c r="W12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X12" s="3">
         <v>3400</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>5</v>
       </c>
@@ -1176,8 +1189,11 @@
       <c r="AE12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1265,13 +1281,16 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>5</v>
@@ -1279,47 +1298,47 @@
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
         <v>900</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>-8400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-9300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>137100</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>29600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3500</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>5</v>
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>5</v>
@@ -1327,18 +1346,18 @@
       <c r="V14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="3">
         <v>1700</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z14" s="3">
         <v>300</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1354,76 +1373,79 @@
       <c r="AE14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E15" s="3">
         <v>2000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4300</v>
-      </c>
-      <c r="I15" s="3">
-        <v>4200</v>
       </c>
       <c r="J15" s="3">
         <v>4200</v>
       </c>
       <c r="K15" s="3">
+        <v>4200</v>
+      </c>
+      <c r="L15" s="3">
         <v>6400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>6600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>4400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>3300</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U15" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W15" s="3">
+      <c r="W15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X15" s="3">
         <v>4300</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>0</v>
+      <c r="Y15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z15" s="3">
         <v>0</v>
@@ -1443,8 +1465,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1473,186 +1498,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E17" s="3">
         <v>35000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>35300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>34000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>39300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>37000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>42300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>41100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>182400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>37300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>72700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>41600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>46800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>39400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>37100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>32100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>54600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>14300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>16600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>27400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>22200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>8300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>8400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>7700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E18" s="3">
         <v>2100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-7200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-6000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-145500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-37700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-16400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-19400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-4000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-8300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-8200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1684,83 +1716,84 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
+      <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>4000</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3">
         <v>16700</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>1200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-800</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>400</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-300</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
@@ -1773,97 +1806,103 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E21" s="3">
         <v>4100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1400</v>
       </c>
-      <c r="G21" s="3">
-        <v>-8200</v>
-      </c>
       <c r="H21" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="I21" s="3">
         <v>-2800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-21000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-137900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-32000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-11800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-16300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-3900</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" s="3">
         <v>7000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>2900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1874,34 +1913,34 @@
         <v>1200</v>
       </c>
       <c r="F22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G22" s="3">
         <v>1100</v>
       </c>
-      <c r="G22" s="3">
-        <v>-3900</v>
-      </c>
       <c r="H22" s="3">
+        <v>800</v>
+      </c>
+      <c r="I22" s="3">
         <v>1300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1700</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M22" s="3">
         <v>1100</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1913,224 +1952,233 @@
         <v>0</v>
       </c>
       <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
         <v>400</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X22" s="3">
         <v>200</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB22" s="3">
         <v>200</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="3" t="s">
-        <v>5</v>
+      <c r="AC22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>0</v>
       </c>
       <c r="AE22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E23" s="3">
         <v>1000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-9600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-8400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-17800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-144300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-38600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-16000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-19900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-8600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-8600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>800</v>
-      </c>
-      <c r="F24" s="3">
-        <v>-200</v>
       </c>
       <c r="G24" s="3">
         <v>-200</v>
       </c>
       <c r="H24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I24" s="3">
         <v>-300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-3400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-900</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>-400</v>
       </c>
       <c r="AA24" s="3">
         <v>-400</v>
       </c>
       <c r="AB24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AC24" s="3">
         <v>-500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
       <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2218,186 +2266,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E26" s="3">
         <v>2100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-8200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-18400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-147700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-6900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-38300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-12500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-20200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-8800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E27" s="3">
         <v>2100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-8200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-18400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-147700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-38300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-12500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-20200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-8800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2485,8 +2542,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2574,8 +2634,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2663,8 +2726,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2752,83 +2818,86 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
+      <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>700</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3">
         <v>-16700</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>-1200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>800</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-400</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>300</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
@@ -2841,97 +2910,103 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E33" s="3">
         <v>2100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-8200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-18400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-147700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-38300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-12500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-20200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-8800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3019,191 +3094,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E35" s="3">
         <v>2100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-8200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-18400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-147700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-38300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-12500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-20200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-8800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42735</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42551</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3235,8 +3319,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3268,97 +3353,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E41" s="3">
         <v>36500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>36900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>36600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>38600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>39200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>43400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>40800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>45900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>41800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>49100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>33600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>39500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>50300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>52100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>52200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>152700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>57500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>63800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3446,97 +3535,103 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E43" s="3">
         <v>12000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>11400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>13900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>13800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>13100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>11200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7400</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>12200</v>
       </c>
       <c r="R43" s="3">
         <v>12200</v>
       </c>
       <c r="S43" s="3">
+        <v>12200</v>
+      </c>
+      <c r="T43" s="3">
         <v>8100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>9100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>9200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>12700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>5300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>9100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4800</v>
-      </c>
-      <c r="AD43" s="3">
-        <v>3500</v>
       </c>
       <c r="AE43" s="3">
         <v>3500</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3561,8 +3656,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3585,225 +3680,234 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T44" s="3">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U44" s="3">
         <v>400</v>
-      </c>
-      <c r="U44" s="3">
-        <v>800</v>
       </c>
       <c r="V44" s="3">
         <v>800</v>
       </c>
       <c r="W44" s="3">
+        <v>800</v>
+      </c>
+      <c r="X44" s="3">
         <v>900</v>
       </c>
-      <c r="X44" s="3">
-        <v>0</v>
-      </c>
       <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="3">
         <v>1200</v>
       </c>
-      <c r="Z44" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB44" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD44" s="3">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE44" s="3">
         <v>100</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E45" s="3">
         <v>4200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3100</v>
-      </c>
-      <c r="K45" s="3">
-        <v>7900</v>
       </c>
       <c r="L45" s="3">
         <v>7900</v>
       </c>
       <c r="M45" s="3">
+        <v>7900</v>
+      </c>
+      <c r="N45" s="3">
         <v>7000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1100</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>1200</v>
       </c>
       <c r="AB45" s="3">
         <v>1200</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>5</v>
+      <c r="AC45" s="3">
+        <v>1200</v>
       </c>
       <c r="AD45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>52800</v>
+      </c>
+      <c r="E46" s="3">
         <v>55500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>53900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>52400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>56500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>55800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>60900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>63100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>67600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>62900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>67400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>49200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>54400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>62500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>68800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>70600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>163500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>70200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>72800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>18000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>18800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>17000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>13800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>9200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>8100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>9600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>8700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>8500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3828,8 +3932,8 @@
       <c r="J47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3852,14 +3956,14 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T47" s="3">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U47" s="3">
         <v>300</v>
-      </c>
-      <c r="U47" s="3">
-        <v>100</v>
       </c>
       <c r="V47" s="3">
         <v>100</v>
@@ -3867,8 +3971,8 @@
       <c r="W47" s="3">
         <v>100</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>5</v>
+      <c r="X47" s="3">
+        <v>100</v>
       </c>
       <c r="Y47" s="3" t="s">
         <v>5</v>
@@ -3876,8 +3980,8 @@
       <c r="Z47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
+      <c r="AA47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB47" s="3">
         <v>0</v>
@@ -3891,186 +3995,195 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E48" s="3">
         <v>7200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2400</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O48" s="3">
+      <c r="O48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P48" s="3">
         <v>3300</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S48" s="3">
+      <c r="S48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T48" s="3">
         <v>2100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E49" s="3">
         <v>18200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>18400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>19600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>20700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>23300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>26800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>29900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>31700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>162900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>174200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>191800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>196500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>200900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>206500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>204300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>7100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>10300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>6800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>7200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>7900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>7400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4158,8 +4271,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4247,13 +4363,16 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1700</v>
+        <v>300</v>
       </c>
       <c r="E52" s="3">
         <v>1700</v>
@@ -4262,46 +4381,46 @@
         <v>1700</v>
       </c>
       <c r="G52" s="3">
-        <v>400</v>
+        <v>1700</v>
       </c>
       <c r="H52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I52" s="3">
         <v>2200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1900</v>
-      </c>
-      <c r="J52" s="3">
-        <v>900</v>
       </c>
       <c r="K52" s="3">
         <v>900</v>
       </c>
       <c r="L52" s="3">
+        <v>900</v>
+      </c>
+      <c r="M52" s="3">
         <v>1800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>13000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>500</v>
-      </c>
-      <c r="T52" s="3">
-        <v>100</v>
       </c>
       <c r="U52" s="3">
         <v>100</v>
@@ -4310,34 +4429,37 @@
         <v>100</v>
       </c>
       <c r="W52" s="3">
+        <v>100</v>
+      </c>
+      <c r="X52" s="3">
         <v>800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>200</v>
       </c>
-      <c r="Z52" s="3">
-        <v>0</v>
-      </c>
       <c r="AA52" s="3">
         <v>0</v>
       </c>
       <c r="AB52" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AC52" s="3">
         <v>200</v>
       </c>
       <c r="AD52" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="AE52" s="3">
         <v>800</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4425,97 +4547,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>77100</v>
+      </c>
+      <c r="E54" s="3">
         <v>82600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>81200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>81400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>87500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>88700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>95000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>96600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>103100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>230100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>246000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>250700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>260900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>276400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>283000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>278800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>173200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>78000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>79900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>24500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>26200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>23100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>22600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>15300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>15800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>17900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>17400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>17600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4547,8 +4675,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4580,105 +4709,109 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E57" s="3">
         <v>7000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6400</v>
-      </c>
-      <c r="L57" s="3">
-        <v>6300</v>
       </c>
       <c r="M57" s="3">
         <v>6300</v>
       </c>
       <c r="N57" s="3">
+        <v>6300</v>
+      </c>
+      <c r="O57" s="3">
         <v>5800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>13400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>12900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>9400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>9100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>900</v>
+      </c>
+      <c r="E58" s="3">
         <v>1000</v>
-      </c>
-      <c r="E58" s="3">
-        <v>800</v>
       </c>
       <c r="F58" s="3">
         <v>800</v>
@@ -4690,11 +4823,11 @@
         <v>800</v>
       </c>
       <c r="I58" s="3">
+        <v>800</v>
+      </c>
+      <c r="J58" s="3">
         <v>400</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -4716,38 +4849,38 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S58" s="3">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T58" s="3">
         <v>100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>300</v>
-      </c>
-      <c r="U58" s="3">
-        <v>500</v>
       </c>
       <c r="V58" s="3">
         <v>500</v>
       </c>
       <c r="W58" s="3">
+        <v>500</v>
+      </c>
+      <c r="X58" s="3">
         <v>900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>300</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB58" s="3" t="s">
-        <v>5</v>
+      <c r="AB58" s="3">
+        <v>0</v>
       </c>
       <c r="AC58" s="3" t="s">
         <v>5</v>
@@ -4758,222 +4891,231 @@
       <c r="AE58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E59" s="3">
         <v>14600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>18400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>16500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>17100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>15100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>14000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>26100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>20300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>21200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>24200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>27800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>28700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>24600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>21200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>7500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>7100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1300</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AE59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E60" s="3">
         <v>31900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>34600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>33200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>36700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>32500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>32300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>31000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>32500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>26700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>27400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>30000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>33000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>33300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>28800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>25500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>17300</v>
-      </c>
-      <c r="T60" s="3">
-        <v>15200</v>
       </c>
       <c r="U60" s="3">
         <v>15200</v>
       </c>
       <c r="V60" s="3">
+        <v>15200</v>
+      </c>
+      <c r="W60" s="3">
         <v>9100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>12300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>49400</v>
+      </c>
+      <c r="E61" s="3">
         <v>48700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>47500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>46600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>45800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>44800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>41500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>28500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>28200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>27900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>27700</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -4990,132 +5132,138 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U61" s="3">
         <v>400</v>
       </c>
       <c r="V61" s="3">
+        <v>400</v>
+      </c>
+      <c r="W61" s="3">
         <v>500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2500</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E62" s="3">
         <v>1900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>21600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>23200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>21900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>400</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W62" s="3">
+      <c r="W62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X62" s="3">
         <v>700</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z62" s="3">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA62" s="3">
         <v>300</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
-      </c>
       <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="3">
         <v>200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>300</v>
-      </c>
-      <c r="AD62" s="3">
-        <v>400</v>
       </c>
       <c r="AE62" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5203,8 +5351,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5292,8 +5443,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5381,97 +5535,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>88300</v>
+      </c>
+      <c r="E66" s="3">
         <v>88400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>91300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>90300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>92100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>86600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>85000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>72000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>82300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>77700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>77000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>33700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>36900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>37200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>32500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>29400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>17700</v>
-      </c>
-      <c r="T66" s="3">
-        <v>15600</v>
       </c>
       <c r="U66" s="3">
         <v>15600</v>
       </c>
       <c r="V66" s="3">
+        <v>15600</v>
+      </c>
+      <c r="W66" s="3">
         <v>9600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>11000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>12900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>10600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5503,8 +5663,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5592,8 +5753,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5681,8 +5845,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5770,8 +5937,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5859,97 +6029,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-317300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-313100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-315200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-313500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-309300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-299900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-291800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-273400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-274900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-127200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-120200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-80900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-76400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-63800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-55100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-51400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-45800</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V72" s="3">
+      <c r="V72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W72" s="3">
         <v>-21900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-23000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-16900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-25300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-14800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-14700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-13000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-10600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-8900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-6100</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6037,8 +6213,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6126,8 +6305,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6215,97 +6397,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E76" s="3">
         <v>-5800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-10200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-8900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-4600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>24600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>152400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>169000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>217000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>224000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>239200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>250400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>249400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>155600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>62400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>64300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>14800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>10200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>11100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6393,191 +6581,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42735</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42551</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E81" s="3">
         <v>2100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-8200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-18400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-147700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-38300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-12500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-20200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-8800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6609,8 +6806,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6618,88 +6816,91 @@
         <v>500</v>
       </c>
       <c r="E83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F83" s="3">
         <v>400</v>
       </c>
       <c r="G83" s="3">
+        <v>400</v>
+      </c>
+      <c r="H83" s="3">
         <v>500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3200</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X83" s="3">
         <v>4700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>6200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>2500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>2400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>2000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6787,8 +6988,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6876,8 +7080,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6965,8 +7172,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7054,8 +7264,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7143,97 +7356,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-6400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>7700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-6300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4600</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X89" s="3">
         <v>6300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>5300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-200</v>
       </c>
-      <c r="AC89" s="3">
-        <v>0</v>
-      </c>
       <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="3">
         <v>-900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7265,86 +7484,87 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>1400</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W91" s="3">
-        <v>-200</v>
+      <c r="W91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X91" s="3">
         <v>-200</v>
       </c>
       <c r="Y91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
       <c r="AC91" s="3">
         <v>0</v>
       </c>
@@ -7352,10 +7572,13 @@
         <v>0</v>
       </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7443,8 +7666,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7532,8 +7758,11 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7541,88 +7770,91 @@
         <v>-900</v>
       </c>
       <c r="E94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1200</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-1800</v>
       </c>
       <c r="J94" s="3">
         <v>-1800</v>
       </c>
       <c r="K94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="L94" s="3">
         <v>-1600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8500</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-4000</v>
       </c>
       <c r="O94" s="3">
         <v>-4000</v>
       </c>
       <c r="P94" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-7900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-94600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1700</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X94" s="3">
         <v>-2900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7654,8 +7886,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7680,8 +7913,8 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7743,8 +7976,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7832,8 +8068,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7921,8 +8160,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8010,8 +8252,11 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8025,256 +8270,265 @@
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>1300</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>27000</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>500</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>-300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>154700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-400</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X100" s="3">
         <v>200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>5700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>5200</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>2500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>3200</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>400</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W101" s="3">
+      <c r="W101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X101" s="3">
         <v>300</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>100</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-100</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
         <v>0</v>
       </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>300</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>4100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-7300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>15500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-10800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-100500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>142400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-6400</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3">
         <v>3200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>3200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-4700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/GAN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GAN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="92">
   <si>
     <t>GAN</t>
   </si>
@@ -656,309 +656,316 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42551</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E8" s="3">
         <v>31700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>37100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>35600</v>
-      </c>
-      <c r="G8" s="3">
-        <v>30700</v>
       </c>
       <c r="H8" s="3">
         <v>30700</v>
       </c>
       <c r="I8" s="3">
+        <v>30700</v>
+      </c>
+      <c r="J8" s="3">
         <v>29800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>33800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>35100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>36900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>32100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>35000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>37500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>30400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>32300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>34400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>27100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>35200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>30000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>14000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5000</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>4800</v>
       </c>
       <c r="AE8" s="3">
         <v>4800</v>
       </c>
       <c r="AF8" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AG8" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E9" s="3">
         <v>10900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>9800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>9200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>9500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>10200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>10000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>9400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>11700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>11500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>18500</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z9" s="3">
+      <c r="Z9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA9" s="3">
         <v>11900</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB9" s="3" t="s">
         <v>5</v>
       </c>
@@ -974,83 +981,86 @@
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E10" s="3">
         <v>20700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>27200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>25300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>21300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>20900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>20600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>24300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>25000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>26900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>22700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>24500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>25800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>18900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>21500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>24000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>18400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>24700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>6400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>11500</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z10" s="3">
+      <c r="Z10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA10" s="3">
         <v>2100</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1066,8 +1076,11 @@
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1100,77 +1113,78 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E12" s="3">
         <v>8000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>8500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>8100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>9600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>8300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>9200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>11200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>9600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>7200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>9000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>7000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>4800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>5200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>11000</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X12" s="3">
+      <c r="X12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y12" s="3">
         <v>3400</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>5</v>
       </c>
@@ -1192,8 +1206,11 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1284,16 +1301,19 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
@@ -1301,47 +1321,47 @@
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
         <v>900</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3">
         <v>-8400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-9300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>137100</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>29600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3500</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
+      <c r="T14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>5</v>
@@ -1349,18 +1369,18 @@
       <c r="W14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y14" s="3">
         <v>1700</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA14" s="3">
         <v>300</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1376,79 +1396,82 @@
       <c r="AF14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4300</v>
-      </c>
-      <c r="J15" s="3">
-        <v>4200</v>
       </c>
       <c r="K15" s="3">
         <v>4200</v>
       </c>
       <c r="L15" s="3">
+        <v>4200</v>
+      </c>
+      <c r="M15" s="3">
         <v>6400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>5900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>6600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>4400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>4100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>4600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>4100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>4000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>3300</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V15" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X15" s="3">
+      <c r="X15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y15" s="3">
         <v>4300</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>0</v>
+      <c r="Z15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA15" s="3">
         <v>0</v>
@@ -1468,8 +1491,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1499,192 +1525,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>34400</v>
+      </c>
+      <c r="E17" s="3">
         <v>34300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>35000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>35300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>34000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>39300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>37000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>42300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>41100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>182400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>37300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>72700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>41600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>46800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>39400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>37100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>32100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>54600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>14300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>16600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>27400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>10400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>22200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>8000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>8400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-6000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-145500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-37700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-7100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-19400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-4000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-8300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-8200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1717,86 +1750,87 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>4000</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
+        <v>16700</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>400</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-700</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J20" s="3">
-        <v>16700</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L20" s="3">
-        <v>1200</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3">
-        <v>-800</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>400</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="Y20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="AA20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-300</v>
       </c>
-      <c r="W20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="X20" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
@@ -1809,100 +1843,106 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-700</v>
+        <v>-3000</v>
       </c>
       <c r="E21" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="F21" s="3">
         <v>4100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1400</v>
       </c>
-      <c r="H21" s="3">
-        <v>-3500</v>
-      </c>
       <c r="I21" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="J21" s="3">
         <v>-2800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-21000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-137900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-32000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-16300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-3900</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y21" s="3">
         <v>7000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>2900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-2100</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1910,40 +1950,40 @@
         <v>1200</v>
       </c>
       <c r="E22" s="3">
-        <v>1200</v>
+        <v>-3400</v>
       </c>
       <c r="F22" s="3">
         <v>1200</v>
       </c>
       <c r="G22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H22" s="3">
         <v>1100</v>
       </c>
-      <c r="H22" s="3">
-        <v>800</v>
-      </c>
       <c r="I22" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="J22" s="3">
         <v>1300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1700</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N22" s="3">
         <v>1100</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1955,230 +1995,239 @@
         <v>0</v>
       </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>400</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y22" s="3">
         <v>200</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AB22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC22" s="3">
         <v>200</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="3" t="s">
-        <v>5</v>
+      <c r="AD22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>0</v>
       </c>
       <c r="AF22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-17800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-144300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-38600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-7100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-19900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-4100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-8600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-8600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>800</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-200</v>
       </c>
       <c r="H24" s="3">
         <v>-200</v>
       </c>
       <c r="I24" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J24" s="3">
         <v>-300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>400</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-900</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>-400</v>
       </c>
       <c r="AB24" s="3">
         <v>-400</v>
       </c>
       <c r="AC24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AD24" s="3">
         <v>-500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
       <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2269,192 +2318,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-8200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-18400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-147700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-6900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-38300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-12500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-8700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-5600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-20200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-8800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-8200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-18400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-147700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-38300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-12500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-8700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-5600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-20200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-8800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2545,8 +2603,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2637,8 +2698,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2729,8 +2793,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2821,86 +2888,89 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="N32" s="3">
+        <v>300</v>
+      </c>
+      <c r="O32" s="3">
+        <v>800</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>700</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-16700</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
+        <v>100</v>
+      </c>
+      <c r="W32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
-        <v>800</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="Y32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Z32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="AA32" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB32" s="3">
         <v>300</v>
       </c>
-      <c r="W32" s="3">
-        <v>100</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>400</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>300</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
@@ -2913,100 +2983,106 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-18400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-147700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-38300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-12500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-8700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-20200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-8800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3097,197 +3173,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-18400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-147700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-38300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-12500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-8700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-20200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-8800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42551</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3320,8 +3405,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3354,100 +3440,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E41" s="3">
         <v>38700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>36500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>36900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>36600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>38600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>39200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>43400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>40800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>45900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>41800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>49100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>33600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>39500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>50300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>52100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>52200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>152700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>57500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>63800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>10300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3538,100 +3628,106 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E43" s="3">
         <v>7000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>12000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>13900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>13800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>13100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>11200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7400</v>
-      </c>
-      <c r="R43" s="3">
-        <v>12200</v>
       </c>
       <c r="S43" s="3">
         <v>12200</v>
       </c>
       <c r="T43" s="3">
+        <v>12200</v>
+      </c>
+      <c r="U43" s="3">
         <v>8100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>9100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>7600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>9200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>12700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>9100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4800</v>
-      </c>
-      <c r="AE43" s="3">
-        <v>3500</v>
       </c>
       <c r="AF43" s="3">
         <v>3500</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3659,8 +3755,8 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3683,231 +3779,240 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U44" s="3">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V44" s="3">
         <v>400</v>
-      </c>
-      <c r="V44" s="3">
-        <v>800</v>
       </c>
       <c r="W44" s="3">
         <v>800</v>
       </c>
       <c r="X44" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y44" s="3">
         <v>900</v>
       </c>
-      <c r="Y44" s="3">
-        <v>0</v>
-      </c>
       <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="3">
         <v>1200</v>
       </c>
-      <c r="AA44" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC44" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE44" s="3">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF44" s="3">
         <v>100</v>
       </c>
-      <c r="AF44" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E45" s="3">
         <v>3900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3100</v>
-      </c>
-      <c r="L45" s="3">
-        <v>7900</v>
       </c>
       <c r="M45" s="3">
         <v>7900</v>
       </c>
       <c r="N45" s="3">
+        <v>7900</v>
+      </c>
+      <c r="O45" s="3">
         <v>7000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1100</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>1200</v>
       </c>
       <c r="AC45" s="3">
         <v>1200</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>5</v>
+      <c r="AD45" s="3">
+        <v>1200</v>
       </c>
       <c r="AE45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>51500</v>
+      </c>
+      <c r="E46" s="3">
         <v>52800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>55500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>53900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>52400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>56500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>55800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>60900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>63100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>67600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>62900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>67400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>49200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>54400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>62500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>68800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>70600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>163500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>70200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>72800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>18000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>18800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>17000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>13800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>9200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>8100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>9600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>8700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>8500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3935,8 +4040,8 @@
       <c r="K47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3959,14 +4064,14 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U47" s="3">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V47" s="3">
         <v>300</v>
-      </c>
-      <c r="V47" s="3">
-        <v>100</v>
       </c>
       <c r="W47" s="3">
         <v>100</v>
@@ -3974,8 +4079,8 @@
       <c r="X47" s="3">
         <v>100</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>5</v>
+      <c r="Y47" s="3">
+        <v>100</v>
       </c>
       <c r="Z47" s="3" t="s">
         <v>5</v>
@@ -3983,8 +4088,8 @@
       <c r="AA47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB47" s="3">
-        <v>0</v>
+      <c r="AB47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC47" s="3">
         <v>0</v>
@@ -3998,192 +4103,201 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E48" s="3">
         <v>6400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2400</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P48" s="3">
+      <c r="P48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q48" s="3">
         <v>3300</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T48" s="3">
+      <c r="T48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U48" s="3">
         <v>2100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E49" s="3">
         <v>16300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>18200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>19600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>20700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>23300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>26800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>29900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>31700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>162900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>174200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>191800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>196500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>200900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>206500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>204300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>10300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>6800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>7700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>7900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>7400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4274,8 +4388,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4366,16 +4483,19 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E52" s="3">
         <v>300</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1700</v>
       </c>
       <c r="F52" s="3">
         <v>1700</v>
@@ -4387,43 +4507,43 @@
         <v>1700</v>
       </c>
       <c r="I52" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J52" s="3">
         <v>2200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1900</v>
-      </c>
-      <c r="K52" s="3">
-        <v>900</v>
       </c>
       <c r="L52" s="3">
         <v>900</v>
       </c>
       <c r="M52" s="3">
+        <v>900</v>
+      </c>
+      <c r="N52" s="3">
         <v>1800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>13000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>500</v>
-      </c>
-      <c r="U52" s="3">
-        <v>100</v>
       </c>
       <c r="V52" s="3">
         <v>100</v>
@@ -4432,34 +4552,37 @@
         <v>100</v>
       </c>
       <c r="X52" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y52" s="3">
         <v>800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>200</v>
       </c>
-      <c r="AA52" s="3">
-        <v>0</v>
-      </c>
       <c r="AB52" s="3">
         <v>0</v>
       </c>
       <c r="AC52" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AD52" s="3">
         <v>200</v>
       </c>
       <c r="AE52" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="AF52" s="3">
         <v>800</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4550,100 +4673,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>75200</v>
+      </c>
+      <c r="E54" s="3">
         <v>77100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>82600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>81200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>81400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>87500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>88700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>95000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>96600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>103100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>230100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>246000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>250700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>260900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>276400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>283000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>278800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>173200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>78000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>79900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>24500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>26200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>23100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>22600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>15300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>15800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>17900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>17400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>17600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>17000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4676,8 +4805,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4710,111 +4840,115 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E57" s="3">
         <v>5600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6400</v>
-      </c>
-      <c r="M57" s="3">
-        <v>6300</v>
       </c>
       <c r="N57" s="3">
         <v>6300</v>
       </c>
       <c r="O57" s="3">
+        <v>6300</v>
+      </c>
+      <c r="P57" s="3">
         <v>5800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>13400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>12900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>9100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E58" s="3">
         <v>900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1000</v>
-      </c>
-      <c r="F58" s="3">
-        <v>800</v>
       </c>
       <c r="G58" s="3">
         <v>800</v>
@@ -4826,11 +4960,11 @@
         <v>800</v>
       </c>
       <c r="J58" s="3">
+        <v>800</v>
+      </c>
+      <c r="K58" s="3">
         <v>400</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -4852,38 +4986,38 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T58" s="3">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U58" s="3">
         <v>100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>300</v>
-      </c>
-      <c r="V58" s="3">
-        <v>500</v>
       </c>
       <c r="W58" s="3">
         <v>500</v>
       </c>
       <c r="X58" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y58" s="3">
         <v>900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>300</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC58" s="3" t="s">
-        <v>5</v>
+      <c r="AC58" s="3">
+        <v>0</v>
       </c>
       <c r="AD58" s="3" t="s">
         <v>5</v>
@@ -4894,231 +5028,240 @@
       <c r="AF58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E59" s="3">
         <v>16200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>14600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>18400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>17100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>26100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>20300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>21200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>24200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>27800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>28700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>24600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>21200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>12600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>7500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>7100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1300</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>32800</v>
+      </c>
+      <c r="E60" s="3">
         <v>31200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>31900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>34600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>33200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>36700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>32500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>32300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>31000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>32500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>27400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>30000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>33000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>33300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>28800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>25500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>17300</v>
-      </c>
-      <c r="U60" s="3">
-        <v>15200</v>
       </c>
       <c r="V60" s="3">
         <v>15200</v>
       </c>
       <c r="W60" s="3">
+        <v>15200</v>
+      </c>
+      <c r="X60" s="3">
         <v>9100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>12300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>50500</v>
+      </c>
+      <c r="E61" s="3">
         <v>49400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>48700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>47500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>46600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>45800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>44800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>41500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>28500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>28200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>27900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>27700</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -5135,135 +5278,141 @@
         <v>0</v>
       </c>
       <c r="U61" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V61" s="3">
         <v>400</v>
       </c>
       <c r="W61" s="3">
+        <v>400</v>
+      </c>
+      <c r="X61" s="3">
         <v>500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2500</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
       <c r="AE61" s="3">
         <v>0</v>
       </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E62" s="3">
         <v>1400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>21600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>23200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>21900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>400</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X62" s="3">
+      <c r="X62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y62" s="3">
         <v>700</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA62" s="3">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB62" s="3">
         <v>300</v>
       </c>
-      <c r="AB62" s="3">
-        <v>0</v>
-      </c>
       <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="3">
         <v>200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>300</v>
-      </c>
-      <c r="AE62" s="3">
-        <v>400</v>
       </c>
       <c r="AF62" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5354,8 +5503,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5446,8 +5598,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5538,100 +5693,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>91600</v>
+      </c>
+      <c r="E66" s="3">
         <v>88300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>88400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>91300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>90300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>92100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>86600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>85000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>72000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>82300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>77700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>77000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>33700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>36900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>37200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>32500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>29400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>17700</v>
-      </c>
-      <c r="U66" s="3">
-        <v>15600</v>
       </c>
       <c r="V66" s="3">
         <v>15600</v>
       </c>
       <c r="W66" s="3">
+        <v>15600</v>
+      </c>
+      <c r="X66" s="3">
         <v>9600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>11000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>12900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>10600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5664,8 +5825,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5756,8 +5918,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5848,8 +6013,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5940,8 +6108,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6032,100 +6203,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-324100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-317300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-313100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-315200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-313500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-309300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-299900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-291800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-273400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-274900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-127200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-120200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-80900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-76400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-63800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-55100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-51400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-45800</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X72" s="3">
         <v>-21900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-23000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-16900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-25300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-14800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-14700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-13000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-10600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-8900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-6100</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6216,8 +6393,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6308,8 +6488,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6400,100 +6583,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="E76" s="3">
         <v>-11100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-5800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-10200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-8900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-4600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>24600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>152400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>169000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>217000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>224000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>239200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>250400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>249400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>155600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>62400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>64300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>14800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>15100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>10200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>12200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>11100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>13000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12500</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6584,197 +6773,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42551</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42369</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-18400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-147700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-38300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-12500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-8700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-20200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-8800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6807,100 +7005,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E83" s="3">
         <v>500</v>
       </c>
       <c r="F83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G83" s="3">
         <v>400</v>
       </c>
       <c r="H83" s="3">
+        <v>400</v>
+      </c>
+      <c r="I83" s="3">
         <v>500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3200</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X83" s="3">
+      <c r="X83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y83" s="3">
         <v>4700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>6200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>2700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>2500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>2400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>2000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6991,8 +7193,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7083,8 +7288,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7175,8 +7383,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7267,8 +7478,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7359,100 +7573,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E89" s="3">
         <v>5700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>7700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-6300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-4600</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X89" s="3">
+      <c r="X89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y89" s="3">
         <v>6300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>5300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-200</v>
       </c>
-      <c r="AD89" s="3">
-        <v>0</v>
-      </c>
       <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="3">
         <v>-900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7485,89 +7705,90 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>1400</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X91" s="3">
-        <v>-200</v>
+      <c r="X91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y91" s="3">
         <v>-200</v>
       </c>
       <c r="Z91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-100</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
       <c r="AD91" s="3">
         <v>0</v>
       </c>
@@ -7575,10 +7796,13 @@
         <v>0</v>
       </c>
       <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7669,8 +7893,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7761,100 +7988,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-900</v>
+        <v>-800</v>
       </c>
       <c r="E94" s="3">
         <v>-900</v>
       </c>
       <c r="F94" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G94" s="3">
         <v>-600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1200</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-1800</v>
       </c>
       <c r="K94" s="3">
         <v>-1800</v>
       </c>
       <c r="L94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="M94" s="3">
         <v>-1600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8500</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-4000</v>
       </c>
       <c r="P94" s="3">
         <v>-4000</v>
       </c>
       <c r="Q94" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-94600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1700</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X94" s="3">
+      <c r="X94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2800</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7887,8 +8120,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7916,8 +8150,8 @@
       <c r="K96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7979,8 +8213,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8071,8 +8308,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8163,8 +8403,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8255,13 +8498,16 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
@@ -8273,262 +8519,271 @@
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>1300</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>27000</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>500</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>-300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>154700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-400</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X100" s="3">
+      <c r="X100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y100" s="3">
         <v>200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>5700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>5200</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>2500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>3200</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>3400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>400</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X101" s="3">
+      <c r="X101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y101" s="3">
         <v>300</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>100</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-100</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
         <v>0</v>
       </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>300</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E102" s="3">
         <v>2300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>15500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-100500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>142400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-6400</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X102" s="3">
+      <c r="X102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y102" s="3">
         <v>3200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>3600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>3200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-4700</v>
       </c>
     </row>
